--- a/Ouroboros - Website Image List.xlsx
+++ b/Ouroboros - Website Image List.xlsx
@@ -43,7 +43,7 @@
     <t>Front view of the lodge on a clear, sunny day with the mountains and river behind. Same camera spot as hero-snow.jpg.</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/infindigital/ouroboros/main/assets/img/new/hero-autumn.jpg</t>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/new/hero-autumn.jpg</t>
   </si>
   <si>
     <t>hero-snow.jpg</t>
@@ -52,7 +52,7 @@
     <t>The same front view of the lodge covered in snow. Same camera spot as hero-autumn.jpg.</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/infindigital/ouroboros/main/assets/img/new/hero-snow.jpg</t>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/new/hero-snow.jpg</t>
   </si>
   <si>
     <t>exterior-autumn.jpg</t>
@@ -64,7 +64,7 @@
     <t>Outside of the property in autumn or summer, with the village and mountains around it. Same camera spot as exterior-snow.jpg.</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/infindigital/ouroboros/main/assets/img/exterior-autumn.jpg</t>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/exterior-autumn.jpg</t>
   </si>
   <si>
     <t>exterior-snow.jpg</t>
@@ -73,7 +73,7 @@
     <t>The same outside view of the property in winter snow. Same camera spot as exterior-autumn.jpg.</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/infindigital/ouroboros/main/assets/img/exterior-snow.jpg</t>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/exterior-snow.jpg</t>
   </si>
   <si>
     <t>suite-view.jpg</t>
@@ -82,7 +82,7 @@
     <t>The Mountain Suite: the red bed with the balcony doors and the mountain view.</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/infindigital/ouroboros/main/assets/img/new/suite-view.jpg</t>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/new/suite-view.jpg</t>
   </si>
   <si>
     <t>room-balcony.jpg</t>
@@ -91,7 +91,7 @@
     <t>The Balcony Room: bed and the floor-to-ceiling windows facing the mountains.</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/infindigital/ouroboros/main/assets/img/room-balcony.jpg</t>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/room-balcony.jpg</t>
   </si>
   <si>
     <t>room-crimson.jpg</t>
@@ -100,7 +100,7 @@
     <t>The Crimson Room: red headboard, armchairs and sitting nook.</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/infindigital/ouroboros/main/assets/img/room-crimson.jpg</t>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/room-crimson.jpg</t>
   </si>
   <si>
     <t>room-crimson-top.jpg</t>
@@ -112,7 +112,7 @@
     <t>The Crimson Room photographed from above or a high corner, showing the bed and linen.</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/infindigital/ouroboros/main/assets/img/room-crimson-top.jpg</t>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/room-crimson-top.jpg</t>
   </si>
   <si>
     <t>room-suite.jpg</t>
@@ -121,7 +121,7 @@
     <t>The Sanctuary room: large bed, sheer curtains and soft daylight.</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/infindigital/ouroboros/main/assets/img/room-suite.jpg</t>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/room-suite.jpg</t>
   </si>
   <si>
     <t>bathtub.jpg</t>
@@ -130,7 +130,7 @@
     <t>The bathtub next to the big window with the river and mountain view.</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/infindigital/ouroboros/main/assets/img/bathtub.jpg</t>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/bathtub.jpg</t>
   </si>
   <si>
     <t>spa-bath.jpg</t>
@@ -139,7 +139,7 @@
     <t>A bathroom with the tub and a mountain view, from a different angle than bathtub.jpg.</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/infindigital/ouroboros/main/assets/img/new/spa-bath.jpg</t>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/new/spa-bath.jpg</t>
   </si>
   <si>
     <t>rose-bath.jpg</t>
@@ -151,7 +151,7 @@
     <t>The scenic bathtub facing the mountains, close-up.</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/infindigital/ouroboros/main/assets/img/new/rose-bath.jpg</t>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/new/rose-bath.jpg</t>
   </si>
   <si>
     <t>firepit-sunset.jpg</t>
@@ -160,7 +160,7 @@
     <t>The terrace bonfire lit at sunset.</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/infindigital/ouroboros/main/assets/img/new/firepit-sunset.jpg</t>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/new/firepit-sunset.jpg</t>
   </si>
   <si>
     <t>snow-firelight.jpg</t>
@@ -169,7 +169,7 @@
     <t>The terrace in snow with the bonfire glowing.</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/infindigital/ouroboros/main/assets/img/new/snow-firelight.jpg</t>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/new/snow-firelight.jpg</t>
   </si>
   <si>
     <t>breakfast-terrace.jpg</t>
@@ -178,7 +178,7 @@
     <t>Breakfast served with the valley view.</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/infindigital/ouroboros/main/assets/img/new/breakfast-terrace.jpg</t>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/new/breakfast-terrace.jpg</t>
   </si>
   <si>
     <t>terrace-lounge.jpg</t>
@@ -187,7 +187,7 @@
     <t>Terrace or seating area at golden hour with the mountains behind.</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/infindigital/ouroboros/main/assets/img/new/terrace-lounge.jpg</t>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/new/terrace-lounge.jpg</t>
   </si>
   <si>
     <t>terrace-river.jpg</t>
@@ -196,7 +196,7 @@
     <t>Terrace or seating area looking out over the river valley.</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/infindigital/ouroboros/main/assets/img/new/terrace-river.jpg</t>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/new/terrace-river.jpg</t>
   </si>
   <si>
     <t>himachali-food.jpg</t>
@@ -205,7 +205,7 @@
     <t>A home-cooked Himachali meal served at the property.</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/infindigital/ouroboros/main/assets/img/stock/himachali-food.jpg</t>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/stock/himachali-food.jpg</t>
   </si>
   <si>
     <t>chandra-valley.jpg</t>
@@ -214,7 +214,7 @@
     <t>The Chandra River winding through the valley near Koksar.</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/infindigital/ouroboros/main/assets/img/chandra-valley.jpg</t>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/chandra-valley.jpg</t>
   </si>
   <si>
     <t>peaks-dusk.jpg</t>
@@ -223,7 +223,7 @@
     <t>Snow peaks around Lahaul glowing at dusk.</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/infindigital/ouroboros/main/assets/img/peaks-dusk.jpg</t>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/peaks-dusk.jpg</t>
   </si>
   <si>
     <t>mountain-pines.jpg</t>
@@ -232,7 +232,7 @@
     <t>The Atal Tunnel or the mountain road leading to Koksar.</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/infindigital/ouroboros/main/assets/img/stock/mountain-pines.jpg</t>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/stock/mountain-pines.jpg</t>
   </si>
   <si>
     <t>lake.jpg</t>
@@ -241,7 +241,7 @@
     <t>Sissu Lake.</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/infindigital/ouroboros/main/assets/img/stock/lake.jpg</t>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/stock/lake.jpg</t>
   </si>
   <si>
     <t>waterfall.jpg</t>
@@ -250,7 +250,7 @@
     <t>Sissu Waterfall.</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/infindigital/ouroboros/main/assets/img/stock/waterfall.jpg</t>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/stock/waterfall.jpg</t>
   </si>
   <si>
     <t>monastery.jpg</t>
@@ -259,7 +259,7 @@
     <t>A monastery in Keylong or nearby.</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/infindigital/ouroboros/main/assets/img/stock/monastery.jpg</t>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/stock/monastery.jpg</t>
   </si>
   <si>
     <t>snow-play.jpg</t>
@@ -268,7 +268,7 @@
     <t>Guests playing in the snow or building a snowman near the property.</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/infindigital/ouroboros/main/assets/img/stock/snow-play.jpg</t>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/stock/snow-play.jpg</t>
   </si>
   <si>
     <t>sunrise.jpg</t>
@@ -277,7 +277,7 @@
     <t>Sunrise or sunset over the mountains, ideally taken from the property.</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/infindigital/ouroboros/main/assets/img/stock/sunrise.jpg</t>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/stock/sunrise.jpg</t>
   </si>
   <si>
     <t>village-walk.jpg</t>
@@ -286,7 +286,7 @@
     <t>A walk on a village trail around Koksar.</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/infindigital/ouroboros/main/assets/img/stock/village-walk.jpg</t>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/stock/village-walk.jpg</t>
   </si>
   <si>
     <t>logo-horizontal.png</t>
@@ -298,7 +298,7 @@
     <t>Main logo (emblem + OUROBOROS HOSPITALITY) in colour, transparent background. PNG or SVG.</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/infindigital/ouroboros/main/assets/img/logo-horizontal.png</t>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/logo-horizontal.png</t>
   </si>
   <si>
     <t>logo-horizontal-light.png</t>
@@ -307,7 +307,7 @@
     <t>The same logo in white and gold for dark backgrounds, transparent background. PNG or SVG.</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/infindigital/ouroboros/main/assets/img/logo-horizontal-light.png</t>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/logo-horizontal-light.png</t>
   </si>
   <si>
     <t>logo-emblem.png</t>
@@ -319,7 +319,7 @@
     <t>The Q emblem on its own (no text), transparent background. PNG or SVG.</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/infindigital/ouroboros/main/assets/img/logo-emblem.png</t>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/logo-emblem.png</t>
   </si>
   <si>
     <t>favicon.png</t>
@@ -331,7 +331,7 @@
     <t>The Q emblem as a small square icon for the browser tab.</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/infindigital/ouroboros/main/assets/img/favicon.png</t>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/favicon.png</t>
   </si>
   <si>
     <t>apple-touch-icon.png</t>
@@ -343,7 +343,7 @@
     <t>The Q emblem as a square icon for phone home screens.</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/infindigital/ouroboros/main/assets/img/apple-touch-icon.png</t>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/apple-touch-icon.png</t>
   </si>
 </sst>
 </file>

--- a/Ouroboros - Website Image List.xlsx
+++ b/Ouroboros - Website Image List.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="261">
   <si>
     <t>Ouroboros Hospitality: website image list</t>
   </si>
@@ -28,163 +28,352 @@
     <t>Size (px)</t>
   </si>
   <si>
-    <t>What the image should be</t>
+    <t>What the image shows</t>
   </si>
   <si>
     <t>Current image link</t>
   </si>
   <si>
-    <t>hero-autumn.jpg</t>
-  </si>
-  <si>
-    <t>2560 x 1440</t>
-  </si>
-  <si>
-    <t>Front view of the lodge on a clear, sunny day with the mountains and river behind. Same camera spot as hero-snow.jpg.</t>
-  </si>
-  <si>
-    <t>https://infindigital-ouroboros.vercel.app/assets/img/new/hero-autumn.jpg</t>
-  </si>
-  <si>
-    <t>hero-snow.jpg</t>
-  </si>
-  <si>
-    <t>The same front view of the lodge covered in snow. Same camera spot as hero-autumn.jpg.</t>
-  </si>
-  <si>
-    <t>https://infindigital-ouroboros.vercel.app/assets/img/new/hero-snow.jpg</t>
-  </si>
-  <si>
-    <t>exterior-autumn.jpg</t>
-  </si>
-  <si>
-    <t>2400 x 1600</t>
-  </si>
-  <si>
-    <t>Outside of the property in autumn or summer, with the village and mountains around it. Same camera spot as exterior-snow.jpg.</t>
-  </si>
-  <si>
-    <t>https://infindigital-ouroboros.vercel.app/assets/img/exterior-autumn.jpg</t>
-  </si>
-  <si>
-    <t>exterior-snow.jpg</t>
-  </si>
-  <si>
-    <t>The same outside view of the property in winter snow. Same camera spot as exterior-autumn.jpg.</t>
-  </si>
-  <si>
-    <t>https://infindigital-ouroboros.vercel.app/assets/img/exterior-snow.jpg</t>
+    <t>Used on</t>
+  </si>
+  <si>
+    <t>hero-red-house.jpg</t>
+  </si>
+  <si>
+    <t>1875 x 839</t>
+  </si>
+  <si>
+    <t>Hero, photo 1: the red lodge on a clear autumn day, mountains behind.</t>
+  </si>
+  <si>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/new/hero-red-house.jpg</t>
+  </si>
+  <si>
+    <t>Home, Stay, Gallery</t>
+  </si>
+  <si>
+    <t>hero-snow-village.jpg</t>
+  </si>
+  <si>
+    <t>1881 x 836</t>
+  </si>
+  <si>
+    <t>Hero, photo 2: the same view of the lodge in heavy snow.</t>
+  </si>
+  <si>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/new/hero-snow-village.jpg</t>
+  </si>
+  <si>
+    <t>bath-petals.jpg</t>
+  </si>
+  <si>
+    <t>1080 x 1616</t>
+  </si>
+  <si>
+    <t>Client photo (DSC00031): the freestanding bathtub and corner window.</t>
+  </si>
+  <si>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/new/bath-petals.jpg</t>
+  </si>
+  <si>
+    <t>Stay, Gallery</t>
+  </si>
+  <si>
+    <t>bathtub-window.jpg</t>
+  </si>
+  <si>
+    <t>1178 x 788</t>
+  </si>
+  <si>
+    <t>Client photo: the freestanding bathtub beside the corner window.</t>
+  </si>
+  <si>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/new/bathtub-window.jpg</t>
+  </si>
+  <si>
+    <t>bathtub.jpg</t>
+  </si>
+  <si>
+    <t>2000 x 1333</t>
+  </si>
+  <si>
+    <t>Client photo (01.jpg): a guest in a bathrobe reading beside the bathtub, big corner window onto the valley.</t>
+  </si>
+  <si>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/bathtub.jpg</t>
+  </si>
+  <si>
+    <t>breakfast-terrace.jpg</t>
+  </si>
+  <si>
+    <t>1254 x 1254</t>
+  </si>
+  <si>
+    <t>AI-GENERATED PLACEHOLDER, please replace with a real photo: Breakfast served with the valley view.</t>
+  </si>
+  <si>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/new/breakfast-terrace.jpg</t>
+  </si>
+  <si>
+    <t>Home, Stay, Experiences</t>
+  </si>
+  <si>
+    <t>chandra-rapids.jpg</t>
+  </si>
+  <si>
+    <t>Client photo (DSC01150): the Chandra River rushing through the valley.</t>
+  </si>
+  <si>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/new/chandra-rapids.jpg</t>
+  </si>
+  <si>
+    <t>Experiences, Gallery</t>
+  </si>
+  <si>
+    <t>chandra-river.jpg</t>
+  </si>
+  <si>
+    <t>1000 x 1328</t>
+  </si>
+  <si>
+    <t>Client photo (IMG20261002120240): the Chandra River over rocks.</t>
+  </si>
+  <si>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/new/chandra-river.jpg</t>
+  </si>
+  <si>
+    <t>Home, Gallery</t>
+  </si>
+  <si>
+    <t>chandra-valley.jpg</t>
+  </si>
+  <si>
+    <t>The Chandra River winding through the valley near Koksar.</t>
+  </si>
+  <si>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/chandra-valley.jpg</t>
+  </si>
+  <si>
+    <t>Home, Stay, Experiences, Gallery, Our Story</t>
+  </si>
+  <si>
+    <t>firepit-sunset.jpg</t>
+  </si>
+  <si>
+    <t>AI-GENERATED PLACEHOLDER, please replace with a real photo: The terrace bonfire lit at sunset.</t>
+  </si>
+  <si>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/new/firepit-sunset.jpg</t>
+  </si>
+  <si>
+    <t>lodge-roadside.jpg</t>
+  </si>
+  <si>
+    <t>1616 x 1080</t>
+  </si>
+  <si>
+    <t>Client photo (DSC00054): the lodge beside the road with horses grazing.</t>
+  </si>
+  <si>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/new/lodge-roadside.jpg</t>
+  </si>
+  <si>
+    <t>Home, Experiences, Gallery</t>
+  </si>
+  <si>
+    <t>peaks-dusk.jpg</t>
+  </si>
+  <si>
+    <t>Snow peaks around Lahaul glowing at dusk.</t>
+  </si>
+  <si>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/peaks-dusk.jpg</t>
+  </si>
+  <si>
+    <t>Home, Gallery, Our Story</t>
+  </si>
+  <si>
+    <t>pir-panjal-peaks.jpg</t>
+  </si>
+  <si>
+    <t>Client photo (DSC00088): snow peaks of the Pir Panjal.</t>
+  </si>
+  <si>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/new/pir-panjal-peaks.jpg</t>
+  </si>
+  <si>
+    <t>riverside-moments.jpg</t>
+  </si>
+  <si>
+    <t>Client photo (DSC01144): guests at a table by the river.</t>
+  </si>
+  <si>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/new/riverside-moments.jpg</t>
+  </si>
+  <si>
+    <t>room-balcony.jpg</t>
+  </si>
+  <si>
+    <t>The Balcony Room: bed and the floor-to-ceiling windows facing the mountains.</t>
+  </si>
+  <si>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/room-balcony.jpg</t>
+  </si>
+  <si>
+    <t>Home, Stay, Gallery, Our Story</t>
+  </si>
+  <si>
+    <t>room-book-flowers.jpg</t>
+  </si>
+  <si>
+    <t>1179 x 782</t>
+  </si>
+  <si>
+    <t>Client photo: a book and dried flowers on the bedside table.</t>
+  </si>
+  <si>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/new/room-book-flowers.jpg</t>
+  </si>
+  <si>
+    <t>room-crimson-top.jpg</t>
+  </si>
+  <si>
+    <t>1280 x 796</t>
+  </si>
+  <si>
+    <t>The Crimson Room photographed from above or a high corner, showing the bed and linen.</t>
+  </si>
+  <si>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/room-crimson-top.jpg</t>
+  </si>
+  <si>
+    <t>room-crimson.jpg</t>
+  </si>
+  <si>
+    <t>1280 x 909</t>
+  </si>
+  <si>
+    <t>The Crimson Room: red headboard, armchairs and sitting nook.</t>
+  </si>
+  <si>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/room-crimson.jpg</t>
+  </si>
+  <si>
+    <t>room-evening.jpg</t>
+  </si>
+  <si>
+    <t>Client photo (DSC01136): a room in warm evening light.</t>
+  </si>
+  <si>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/new/room-evening.jpg</t>
+  </si>
+  <si>
+    <t>room-morning-chai.jpg</t>
+  </si>
+  <si>
+    <t>Client photo (DSC00030): guests having tea in a room by the window.</t>
+  </si>
+  <si>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/new/room-morning-chai.jpg</t>
+  </si>
+  <si>
+    <t>room-suite.jpg</t>
+  </si>
+  <si>
+    <t>2000 x 1515</t>
+  </si>
+  <si>
+    <t>The Sanctuary room: large bed, sheer curtains and soft daylight.</t>
+  </si>
+  <si>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/room-suite.jpg</t>
+  </si>
+  <si>
+    <t>rose-bath.jpg</t>
+  </si>
+  <si>
+    <t>Client photo (DSC00033): the bathtub with rose petals by the window.</t>
+  </si>
+  <si>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/new/rose-bath.jpg</t>
+  </si>
+  <si>
+    <t>sitting-corner.jpg</t>
+  </si>
+  <si>
+    <t>Client photo (DSC01140): armchairs and table in the sitting corner.</t>
+  </si>
+  <si>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/new/sitting-corner.jpg</t>
+  </si>
+  <si>
+    <t>snow-firelight.jpg</t>
+  </si>
+  <si>
+    <t>AI-GENERATED PLACEHOLDER, please replace with a real photo: The terrace in snow with the bonfire glowing.</t>
+  </si>
+  <si>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/new/snow-firelight.jpg</t>
+  </si>
+  <si>
+    <t>Home</t>
+  </si>
+  <si>
+    <t>spa-bath.jpg</t>
+  </si>
+  <si>
+    <t>1536 x 1024</t>
+  </si>
+  <si>
+    <t>AI-GENERATED PLACEHOLDER, please replace with a real photo: A bathroom with the tub and a mountain view, from a different angle than bathtub.jpg.</t>
+  </si>
+  <si>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/new/spa-bath.jpg</t>
+  </si>
+  <si>
+    <t>Stay</t>
+  </si>
+  <si>
+    <t>stars-lodge-tall.jpg</t>
+  </si>
+  <si>
+    <t>824 x 1280</t>
+  </si>
+  <si>
+    <t>Client photo: the lodge and a starry sky, tall crop.</t>
+  </si>
+  <si>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/new/stars-lodge-tall.jpg</t>
+  </si>
+  <si>
+    <t>stars-lodge.jpg</t>
+  </si>
+  <si>
+    <t>758 x 1040</t>
+  </si>
+  <si>
+    <t>Client photo: the lodge lit up under the Milky Way.</t>
+  </si>
+  <si>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/new/stars-lodge.jpg</t>
   </si>
   <si>
     <t>suite-view.jpg</t>
   </si>
   <si>
-    <t>The Mountain Suite: the red bed with the balcony doors and the mountain view.</t>
+    <t>AI-GENERATED PLACEHOLDER, please replace with a real photo: The Mountain Suite: the red bed with the balcony doors and the mountain view.</t>
   </si>
   <si>
     <t>https://infindigital-ouroboros.vercel.app/assets/img/new/suite-view.jpg</t>
   </si>
   <si>
-    <t>room-balcony.jpg</t>
-  </si>
-  <si>
-    <t>The Balcony Room: bed and the floor-to-ceiling windows facing the mountains.</t>
-  </si>
-  <si>
-    <t>https://infindigital-ouroboros.vercel.app/assets/img/room-balcony.jpg</t>
-  </si>
-  <si>
-    <t>room-crimson.jpg</t>
-  </si>
-  <si>
-    <t>The Crimson Room: red headboard, armchairs and sitting nook.</t>
-  </si>
-  <si>
-    <t>https://infindigital-ouroboros.vercel.app/assets/img/room-crimson.jpg</t>
-  </si>
-  <si>
-    <t>room-crimson-top.jpg</t>
-  </si>
-  <si>
-    <t>1600 x 2000</t>
-  </si>
-  <si>
-    <t>The Crimson Room photographed from above or a high corner, showing the bed and linen.</t>
-  </si>
-  <si>
-    <t>https://infindigital-ouroboros.vercel.app/assets/img/room-crimson-top.jpg</t>
-  </si>
-  <si>
-    <t>room-suite.jpg</t>
-  </si>
-  <si>
-    <t>The Sanctuary room: large bed, sheer curtains and soft daylight.</t>
-  </si>
-  <si>
-    <t>https://infindigital-ouroboros.vercel.app/assets/img/room-suite.jpg</t>
-  </si>
-  <si>
-    <t>bathtub.jpg</t>
-  </si>
-  <si>
-    <t>The bathtub next to the big window with the river and mountain view.</t>
-  </si>
-  <si>
-    <t>https://infindigital-ouroboros.vercel.app/assets/img/bathtub.jpg</t>
-  </si>
-  <si>
-    <t>spa-bath.jpg</t>
-  </si>
-  <si>
-    <t>A bathroom with the tub and a mountain view, from a different angle than bathtub.jpg.</t>
-  </si>
-  <si>
-    <t>https://infindigital-ouroboros.vercel.app/assets/img/new/spa-bath.jpg</t>
-  </si>
-  <si>
-    <t>rose-bath.jpg</t>
-  </si>
-  <si>
-    <t>2000 x 2000</t>
-  </si>
-  <si>
-    <t>The scenic bathtub facing the mountains, close-up.</t>
-  </si>
-  <si>
-    <t>https://infindigital-ouroboros.vercel.app/assets/img/new/rose-bath.jpg</t>
-  </si>
-  <si>
-    <t>firepit-sunset.jpg</t>
-  </si>
-  <si>
-    <t>The terrace bonfire lit at sunset.</t>
-  </si>
-  <si>
-    <t>https://infindigital-ouroboros.vercel.app/assets/img/new/firepit-sunset.jpg</t>
-  </si>
-  <si>
-    <t>snow-firelight.jpg</t>
-  </si>
-  <si>
-    <t>The terrace in snow with the bonfire glowing.</t>
-  </si>
-  <si>
-    <t>https://infindigital-ouroboros.vercel.app/assets/img/new/snow-firelight.jpg</t>
-  </si>
-  <si>
-    <t>breakfast-terrace.jpg</t>
-  </si>
-  <si>
-    <t>Breakfast served with the valley view.</t>
-  </si>
-  <si>
-    <t>https://infindigital-ouroboros.vercel.app/assets/img/new/breakfast-terrace.jpg</t>
+    <t>Home, Stay</t>
   </si>
   <si>
     <t>terrace-lounge.jpg</t>
   </si>
   <si>
-    <t>Terrace or seating area at golden hour with the mountains behind.</t>
+    <t>AI-GENERATED PLACEHOLDER, please replace with a real photo: Terrace or seating area at golden hour with the mountains behind.</t>
   </si>
   <si>
     <t>https://infindigital-ouroboros.vercel.app/assets/img/new/terrace-lounge.jpg</t>
@@ -193,133 +382,376 @@
     <t>terrace-river.jpg</t>
   </si>
   <si>
-    <t>Terrace or seating area looking out over the river valley.</t>
+    <t>1920 x 768</t>
+  </si>
+  <si>
+    <t>AI-GENERATED PLACEHOLDER, please replace with a real photo: Terrace or seating area looking out over the river valley.</t>
   </si>
   <si>
     <t>https://infindigital-ouroboros.vercel.app/assets/img/new/terrace-river.jpg</t>
   </si>
   <si>
+    <t>Contact</t>
+  </si>
+  <si>
+    <t>valley-trail.jpg</t>
+  </si>
+  <si>
+    <t>Client photo (IMG20260825132743): green slopes and a trail above the valley.</t>
+  </si>
+  <si>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/new/valley-trail.jpg</t>
+  </si>
+  <si>
+    <t>valley-view.jpg</t>
+  </si>
+  <si>
+    <t>Client photo (DSC00091): the valley and peaks from the property.</t>
+  </si>
+  <si>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/new/valley-view.jpg</t>
+  </si>
+  <si>
+    <t>Home, Stay, Experiences, Gallery</t>
+  </si>
+  <si>
+    <t>valley-waterfall.jpg</t>
+  </si>
+  <si>
+    <t>1000 x 1778</t>
+  </si>
+  <si>
+    <t>Client video still (VID20260825135523): the Hidden Waterfall, Koksar. Shown before the waterfall clip plays.</t>
+  </si>
+  <si>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/new/valley-waterfall.jpg</t>
+  </si>
+  <si>
+    <t>by-the-chandra.jpg</t>
+  </si>
+  <si>
+    <t>1200 x 1600</t>
+  </si>
+  <si>
+    <t>Client photo (IMG20261002115619): a guest beside the river.</t>
+  </si>
+  <si>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/gallery/by-the-chandra.jpg</t>
+  </si>
+  <si>
+    <t>Gallery</t>
+  </si>
+  <si>
+    <t>clouds-over-peaks.jpg</t>
+  </si>
+  <si>
+    <t>Client photo (DSC01103): clouds over snow peaks.</t>
+  </si>
+  <si>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/gallery/clouds-over-peaks.jpg</t>
+  </si>
+  <si>
+    <t>fresh-snow-peak.jpg</t>
+  </si>
+  <si>
+    <t>Client photo (DSC01070): a snow covered summit.</t>
+  </si>
+  <si>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/gallery/fresh-snow-peak.jpg</t>
+  </si>
+  <si>
+    <t>guest-valley-view.jpg</t>
+  </si>
+  <si>
+    <t>960 x 1280</t>
+  </si>
+  <si>
+    <t>Client photo (PHOTO-2026-10-23-16-30-03 (1)): a guest in a shawl with the valley behind.</t>
+  </si>
+  <si>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/gallery/guest-valley-view.jpg</t>
+  </si>
+  <si>
+    <t>koksar-roadside.jpg</t>
+  </si>
+  <si>
+    <t>Client photo (PHOTO-2026-10-23-16-30-04 (2)): prayer flags and a tractor by the road.</t>
+  </si>
+  <si>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/gallery/koksar-roadside.jpg</t>
+  </si>
+  <si>
+    <t>lodge-front.jpg</t>
+  </si>
+  <si>
+    <t>1280 x 960</t>
+  </si>
+  <si>
+    <t>Client photo (PHOTO-2026-10-23-16-30-04 (1)): front of the lodge under a blue sky.</t>
+  </si>
+  <si>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/gallery/lodge-front.jpg</t>
+  </si>
+  <si>
+    <t>lodge-sunburst.jpg</t>
+  </si>
+  <si>
+    <t>Client photo (PHOTO-2026-10-23-16-30-03): the sun over the lodge.</t>
+  </si>
+  <si>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/gallery/lodge-sunburst.jpg</t>
+  </si>
+  <si>
+    <t>misty-peaks.jpg</t>
+  </si>
+  <si>
+    <t>Client photo (DSC01060): mist and fresh snow on the peaks.</t>
+  </si>
+  <si>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/gallery/misty-peaks.jpg</t>
+  </si>
+  <si>
+    <t>pink-dusk-peak.jpg</t>
+  </si>
+  <si>
+    <t>Client photo (DSC01119): a peak glowing pink at dusk.</t>
+  </si>
+  <si>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/gallery/pink-dusk-peak.jpg</t>
+  </si>
+  <si>
+    <t>pizza-night.jpg</t>
+  </si>
+  <si>
+    <t>Client photo (DSC00005): pizza at the table.</t>
+  </si>
+  <si>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/gallery/pizza-night.jpg</t>
+  </si>
+  <si>
+    <t>riverside-pup.jpg</t>
+  </si>
+  <si>
+    <t>Client photo (DSC01167): a guest with a puppy by the river.</t>
+  </si>
+  <si>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/gallery/riverside-pup.jpg</t>
+  </si>
+  <si>
+    <t>riverside-tea.jpg</t>
+  </si>
+  <si>
+    <t>Client photo (DSC01162): a couple at a table by the river.</t>
+  </si>
+  <si>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/gallery/riverside-tea.jpg</t>
+  </si>
+  <si>
+    <t>rocky-valley.jpg</t>
+  </si>
+  <si>
+    <t>Client photo (DSC01154): a rocky valley.</t>
+  </si>
+  <si>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/gallery/rocky-valley.jpg</t>
+  </si>
+  <si>
+    <t>snow-peaks-trees.jpg</t>
+  </si>
+  <si>
+    <t>Client photo (DSC00074): snow peaks behind autumn trees.</t>
+  </si>
+  <si>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/gallery/snow-peaks-trees.jpg</t>
+  </si>
+  <si>
+    <t>sun-on-the-face.jpg</t>
+  </si>
+  <si>
+    <t>Client photo (IMG20261002115554): a guest in the sun.</t>
+  </si>
+  <si>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/gallery/sun-on-the-face.jpg</t>
+  </si>
+  <si>
+    <t>sunset-guest.jpg</t>
+  </si>
+  <si>
+    <t>Client photo (DSC01112): a guest at sunset.</t>
+  </si>
+  <si>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/gallery/sunset-guest.jpg</t>
+  </si>
+  <si>
+    <t>valley-fields.jpg</t>
+  </si>
+  <si>
+    <t>Client photo (PHOTO-2026-10-23-16-30-04): fields and storm clouds in the valley.</t>
+  </si>
+  <si>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/gallery/valley-fields.jpg</t>
+  </si>
+  <si>
+    <t>violet-dusk.jpg</t>
+  </si>
+  <si>
+    <t>Client photo (DSC01129): violet sky over a ridge.</t>
+  </si>
+  <si>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/gallery/violet-dusk.jpg</t>
+  </si>
+  <si>
+    <t>waterfall-guest.jpg</t>
+  </si>
+  <si>
+    <t>1204 x 1600</t>
+  </si>
+  <si>
+    <t>Client photo (IMG20260825135658): a guest at the waterfall.</t>
+  </si>
+  <si>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/gallery/waterfall-guest.jpg</t>
+  </si>
+  <si>
+    <t>chandratal.jpg</t>
+  </si>
+  <si>
+    <t>1000 x 1334</t>
+  </si>
+  <si>
+    <t>STOCK PLACEHOLDER, please replace with a real photo: Chandratal Lake, 76 km away.</t>
+  </si>
+  <si>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/stock/chandratal.jpg</t>
+  </si>
+  <si>
     <t>himachali-food.jpg</t>
   </si>
   <si>
-    <t>A home-cooked Himachali meal served at the property.</t>
+    <t>1000 x 1333</t>
+  </si>
+  <si>
+    <t>STOCK PLACEHOLDER, please replace with a real photo: A home-cooked Himachali meal served at the property.</t>
   </si>
   <si>
     <t>https://infindigital-ouroboros.vercel.app/assets/img/stock/himachali-food.jpg</t>
   </si>
   <si>
-    <t>chandra-valley.jpg</t>
-  </si>
-  <si>
-    <t>The Chandra River winding through the valley near Koksar.</t>
-  </si>
-  <si>
-    <t>https://infindigital-ouroboros.vercel.app/assets/img/chandra-valley.jpg</t>
-  </si>
-  <si>
-    <t>peaks-dusk.jpg</t>
-  </si>
-  <si>
-    <t>Snow peaks around Lahaul glowing at dusk.</t>
-  </si>
-  <si>
-    <t>https://infindigital-ouroboros.vercel.app/assets/img/peaks-dusk.jpg</t>
+    <t>Stay, Experiences</t>
+  </si>
+  <si>
+    <t>lake.jpg</t>
+  </si>
+  <si>
+    <t>1400 x 933</t>
+  </si>
+  <si>
+    <t>STOCK PLACEHOLDER, please replace with a real photo: Sissu Lake.</t>
+  </si>
+  <si>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/stock/lake.jpg</t>
+  </si>
+  <si>
+    <t>Home, Experiences</t>
+  </si>
+  <si>
+    <t>monastery.jpg</t>
+  </si>
+  <si>
+    <t>1000 x 667</t>
+  </si>
+  <si>
+    <t>STOCK PLACEHOLDER, please replace with a real photo: A monastery in Keylong or nearby.</t>
+  </si>
+  <si>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/stock/monastery.jpg</t>
   </si>
   <si>
     <t>mountain-pines.jpg</t>
   </si>
   <si>
-    <t>The Atal Tunnel or the mountain road leading to Koksar.</t>
+    <t>STOCK PLACEHOLDER, please replace with a real photo: The Atal Tunnel or the mountain road leading to Koksar.</t>
   </si>
   <si>
     <t>https://infindigital-ouroboros.vercel.app/assets/img/stock/mountain-pines.jpg</t>
   </si>
   <si>
-    <t>lake.jpg</t>
-  </si>
-  <si>
-    <t>Sissu Lake.</t>
-  </si>
-  <si>
-    <t>https://infindigital-ouroboros.vercel.app/assets/img/stock/lake.jpg</t>
+    <t>snow-play.jpg</t>
+  </si>
+  <si>
+    <t>STOCK PLACEHOLDER, please replace with a real photo: Guests playing in the snow or building a snowman near the property.</t>
+  </si>
+  <si>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/stock/snow-play.jpg</t>
+  </si>
+  <si>
+    <t>Experiences</t>
+  </si>
+  <si>
+    <t>sunrise.jpg</t>
+  </si>
+  <si>
+    <t>Client photo (DSC01110): golden clouds over the peaks at sunrise.</t>
+  </si>
+  <si>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/stock/sunrise.jpg</t>
   </si>
   <si>
     <t>waterfall.jpg</t>
   </si>
   <si>
-    <t>Sissu Waterfall.</t>
+    <t>STOCK PLACEHOLDER, please replace with a real photo: Sissu Waterfall.</t>
   </si>
   <si>
     <t>https://infindigital-ouroboros.vercel.app/assets/img/stock/waterfall.jpg</t>
   </si>
   <si>
-    <t>monastery.jpg</t>
-  </si>
-  <si>
-    <t>A monastery in Keylong or nearby.</t>
-  </si>
-  <si>
-    <t>https://infindigital-ouroboros.vercel.app/assets/img/stock/monastery.jpg</t>
-  </si>
-  <si>
-    <t>snow-play.jpg</t>
-  </si>
-  <si>
-    <t>Guests playing in the snow or building a snowman near the property.</t>
-  </si>
-  <si>
-    <t>https://infindigital-ouroboros.vercel.app/assets/img/stock/snow-play.jpg</t>
-  </si>
-  <si>
-    <t>sunrise.jpg</t>
-  </si>
-  <si>
-    <t>Sunrise or sunset over the mountains, ideally taken from the property.</t>
-  </si>
-  <si>
-    <t>https://infindigital-ouroboros.vercel.app/assets/img/stock/sunrise.jpg</t>
-  </si>
-  <si>
-    <t>village-walk.jpg</t>
-  </si>
-  <si>
-    <t>A walk on a village trail around Koksar.</t>
-  </si>
-  <si>
-    <t>https://infindigital-ouroboros.vercel.app/assets/img/stock/village-walk.jpg</t>
-  </si>
-  <si>
-    <t>logo-horizontal.png</t>
-  </si>
-  <si>
-    <t>1200 x 293</t>
-  </si>
-  <si>
-    <t>Main logo (emblem + OUROBOROS HOSPITALITY) in colour, transparent background. PNG or SVG.</t>
-  </si>
-  <si>
-    <t>https://infindigital-ouroboros.vercel.app/assets/img/logo-horizontal.png</t>
-  </si>
-  <si>
-    <t>logo-horizontal-light.png</t>
-  </si>
-  <si>
-    <t>The same logo in white and gold for dark backgrounds, transparent background. PNG or SVG.</t>
-  </si>
-  <si>
-    <t>https://infindigital-ouroboros.vercel.app/assets/img/logo-horizontal-light.png</t>
-  </si>
-  <si>
-    <t>logo-emblem.png</t>
-  </si>
-  <si>
-    <t>800 x 800</t>
-  </si>
-  <si>
-    <t>The Q emblem on its own (no text), transparent background. PNG or SVG.</t>
-  </si>
-  <si>
-    <t>https://infindigital-ouroboros.vercel.app/assets/img/logo-emblem.png</t>
+    <t>koksar-ride-poster.jpg</t>
+  </si>
+  <si>
+    <t>720 x 1280</t>
+  </si>
+  <si>
+    <t>Still frame shown before the video starts playing.</t>
+  </si>
+  <si>
+    <t>https://infindigital-ouroboros.vercel.app/assets/video/koksar-ride-poster.jpg</t>
+  </si>
+  <si>
+    <t>koksar-ride.mp4</t>
+  </si>
+  <si>
+    <t>VIDEO, client reel: cycling through the valley ("On the road" section).</t>
+  </si>
+  <si>
+    <t>https://infindigital-ouroboros.vercel.app/assets/video/koksar-ride.mp4</t>
+  </si>
+  <si>
+    <t>valley-waterfall.mp4</t>
+  </si>
+  <si>
+    <t>540 x 960</t>
+  </si>
+  <si>
+    <t>VIDEO, client clip: the Hidden Waterfall, Koksar. 7 second silent loop.</t>
+  </si>
+  <si>
+    <t>https://infindigital-ouroboros.vercel.app/assets/video/valley-waterfall.mp4</t>
+  </si>
+  <si>
+    <t>apple-touch-icon.png</t>
+  </si>
+  <si>
+    <t>180 x 180</t>
+  </si>
+  <si>
+    <t>The ring logo as a square icon for phone home screens.</t>
+  </si>
+  <si>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/apple-touch-icon.png</t>
+  </si>
+  <si>
+    <t>Home, Stay, Experiences, Gallery, Our Story, Contact</t>
   </si>
   <si>
     <t>favicon.png</t>
@@ -328,22 +760,43 @@
     <t>64 x 64</t>
   </si>
   <si>
-    <t>The Q emblem as a small square icon for the browser tab.</t>
+    <t>The ring logo as a small square icon for the browser tab.</t>
   </si>
   <si>
     <t>https://infindigital-ouroboros.vercel.app/assets/img/favicon.png</t>
   </si>
   <si>
-    <t>apple-touch-icon.png</t>
-  </si>
-  <si>
-    <t>180 x 180</t>
-  </si>
-  <si>
-    <t>The Q emblem as a square icon for phone home screens.</t>
-  </si>
-  <si>
-    <t>https://infindigital-ouroboros.vercel.app/assets/img/apple-touch-icon.png</t>
+    <t>logo-badge.png</t>
+  </si>
+  <si>
+    <t>320 x 320</t>
+  </si>
+  <si>
+    <t>The red ring logo on a round cream badge (header, over photos).</t>
+  </si>
+  <si>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/logo-badge.png</t>
+  </si>
+  <si>
+    <t>logo-ring-cream.png</t>
+  </si>
+  <si>
+    <t>520 x 520</t>
+  </si>
+  <si>
+    <t>The ring logo in cream, transparent background (footer).</t>
+  </si>
+  <si>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/logo-ring-cream.png</t>
+  </si>
+  <si>
+    <t>logo-ring-red.png</t>
+  </si>
+  <si>
+    <t>The Ouroboros brush-ring logo in red, transparent background (header after scrolling, Our Story page).</t>
+  </si>
+  <si>
+    <t>https://infindigital-ouroboros.vercel.app/assets/img/logo-ring-red.png</t>
   </si>
 </sst>
 </file>
@@ -386,7 +839,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -396,11 +849,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA11F21"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBF6EF"/>
       </patternFill>
     </fill>
   </fills>
@@ -431,7 +879,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -450,21 +898,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -809,14 +1242,15 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:F71"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="70" customWidth="1"/>
     <col min="5" max="5" width="62" customWidth="1"/>
+    <col min="6" max="6" width="34" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -828,565 +1262,1384 @@
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
     </row>
-    <row r="3" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+    <row r="3" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F3" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>1</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
+        <v>10</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
         <v>2</v>
       </c>
-      <c r="B5" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="11" t="s">
+      <c r="B5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>3</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
+        <v>19</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
         <v>4</v>
       </c>
-      <c r="B7" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>5</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
+        <v>28</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
         <v>6</v>
       </c>
-      <c r="B9" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>7</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="8">
+        <v>36</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="3">
         <v>8</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B11" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>9</v>
       </c>
       <c r="B12" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="3">
+        <v>10</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="F13" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C12" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="8">
-        <v>10</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E13" s="12" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>11</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="8">
+        <v>53</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="3">
         <v>12</v>
       </c>
-      <c r="B15" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="E15" s="12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B15" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>13</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="8">
+        <v>61</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="3">
         <v>14</v>
       </c>
-      <c r="B17" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="E17" s="12" t="s">
+      <c r="B17" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D17" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>15</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="8">
+        <v>67</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="3">
         <v>16</v>
       </c>
-      <c r="B19" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="D19" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="E19" s="12" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B19" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>17</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>7</v>
+        <v>74</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="8">
+        <v>76</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="3">
         <v>18</v>
       </c>
-      <c r="B21" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="D21" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="E21" s="12" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B21" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>19</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="8">
+        <v>83</v>
+      </c>
+      <c r="F22" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B23" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C23" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="D23" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="E23" s="12" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="3">
+        <v>20</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>21</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>30</v>
+        <v>88</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="8">
+        <v>90</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="3">
         <v>22</v>
       </c>
-      <c r="B25" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="C25" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="D25" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="E25" s="12" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B25" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>23</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="C26" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="3">
+        <v>24</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C27" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D26" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="8">
-        <v>24</v>
-      </c>
-      <c r="B27" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="C27" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="D27" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="E27" s="12" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D27" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>25</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>30</v>
+        <v>102</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="8">
+        <v>104</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="3">
         <v>26</v>
       </c>
-      <c r="B29" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C29" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="D29" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="E29" s="12" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B29" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>27</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="C30" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="3">
+        <v>28</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C31" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D30" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="8">
-        <v>28</v>
-      </c>
-      <c r="B31" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="C31" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="D31" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="E31" s="12" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D31" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>29</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>95</v>
+        <v>118</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>92</v>
+        <v>30</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="8">
+        <v>120</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="3">
         <v>30</v>
       </c>
-      <c r="B33" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="C33" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="D33" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="E33" s="12" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B33" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>31</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>103</v>
+        <v>39</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>104</v>
+        <v>127</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="8">
+        <v>128</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="3">
         <v>32</v>
       </c>
-      <c r="B35" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="C35" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="D35" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="E35" s="12" t="s">
-        <v>109</v>
+      <c r="B35" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="3">
+        <v>33</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="3">
+        <v>34</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="F37" s="6" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="3">
+        <v>35</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="3">
+        <v>36</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="3">
+        <v>37</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="3">
+        <v>38</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="3">
+        <v>39</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="3">
+        <v>40</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="F43" s="6" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="3">
+        <v>41</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="3">
+        <v>42</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="F45" s="6" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="3">
+        <v>43</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="3">
+        <v>44</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="F47" s="6" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="3">
+        <v>45</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="F48" s="6" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="3">
+        <v>46</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="E49" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="F49" s="6" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="3">
+        <v>47</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="3">
+        <v>48</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="E51" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="F51" s="6" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="3">
+        <v>49</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="E52" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="3">
+        <v>50</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D53" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="F53" s="6" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="3">
+        <v>51</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="E54" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="3">
+        <v>52</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="D55" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="F55" s="6" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="3">
+        <v>53</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="E56" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="F56" s="6" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="3">
+        <v>54</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="D57" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="E57" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="F57" s="6" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="3">
+        <v>55</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="D58" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="E58" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="F58" s="6" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="3">
+        <v>56</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="D59" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="E59" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="F59" s="6" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="3">
+        <v>57</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="D60" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="E60" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="3">
+        <v>58</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="D61" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="E61" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="F61" s="6" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="3">
+        <v>59</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D62" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="E62" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="F62" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="3">
+        <v>60</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="E63" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="F63" s="6" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="3">
+        <v>61</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="D64" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="E64" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="F64" s="6" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="3">
+        <v>62</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="D65" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="E65" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="F65" s="6" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="3">
+        <v>63</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="D66" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="E66" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="F66" s="6" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="3">
+        <v>64</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="D67" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="E67" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="F67" s="6" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="3">
+        <v>65</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="D68" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="E68" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="F68" s="6" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="3">
+        <v>66</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="D69" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="E69" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="F69" s="6" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="3">
+        <v>67</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="D70" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="E70" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="F70" s="6" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="3">
+        <v>68</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="C71" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="D71" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="E71" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="F71" s="6" t="s">
+        <v>245</v>
       </c>
     </row>
   </sheetData>
@@ -1426,7 +2679,43 @@
     <hyperlink ref="E33" r:id="rId30"/>
     <hyperlink ref="E34" r:id="rId31"/>
     <hyperlink ref="E35" r:id="rId32"/>
+    <hyperlink ref="E36" r:id="rId33"/>
+    <hyperlink ref="E37" r:id="rId34"/>
+    <hyperlink ref="E38" r:id="rId35"/>
+    <hyperlink ref="E39" r:id="rId36"/>
+    <hyperlink ref="E40" r:id="rId37"/>
+    <hyperlink ref="E41" r:id="rId38"/>
+    <hyperlink ref="E42" r:id="rId39"/>
+    <hyperlink ref="E43" r:id="rId40"/>
+    <hyperlink ref="E44" r:id="rId41"/>
+    <hyperlink ref="E45" r:id="rId42"/>
+    <hyperlink ref="E46" r:id="rId43"/>
+    <hyperlink ref="E47" r:id="rId44"/>
+    <hyperlink ref="E48" r:id="rId45"/>
+    <hyperlink ref="E49" r:id="rId46"/>
+    <hyperlink ref="E50" r:id="rId47"/>
+    <hyperlink ref="E51" r:id="rId48"/>
+    <hyperlink ref="E52" r:id="rId49"/>
+    <hyperlink ref="E53" r:id="rId50"/>
+    <hyperlink ref="E54" r:id="rId51"/>
+    <hyperlink ref="E55" r:id="rId52"/>
+    <hyperlink ref="E56" r:id="rId53"/>
+    <hyperlink ref="E57" r:id="rId54"/>
+    <hyperlink ref="E58" r:id="rId55"/>
+    <hyperlink ref="E59" r:id="rId56"/>
+    <hyperlink ref="E60" r:id="rId57"/>
+    <hyperlink ref="E61" r:id="rId58"/>
+    <hyperlink ref="E62" r:id="rId59"/>
+    <hyperlink ref="E63" r:id="rId60"/>
+    <hyperlink ref="E64" r:id="rId61"/>
+    <hyperlink ref="E65" r:id="rId62"/>
+    <hyperlink ref="E66" r:id="rId63"/>
+    <hyperlink ref="E67" r:id="rId64"/>
+    <hyperlink ref="E68" r:id="rId65"/>
+    <hyperlink ref="E69" r:id="rId66"/>
+    <hyperlink ref="E70" r:id="rId67"/>
+    <hyperlink ref="E71" r:id="rId68"/>
   </hyperlinks>
-  <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>